--- a/docs/list.xlsx
+++ b/docs/list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t xml:space="preserve">Base Image</t>
   </si>
@@ -39,6 +39,9 @@
     <t xml:space="preserve">python</t>
   </si>
   <si>
+    <t xml:space="preserve">git</t>
+  </si>
+  <si>
     <t xml:space="preserve">version</t>
   </si>
   <si>
@@ -51,26 +54,39 @@
     <t xml:space="preserve">3.12-slim</t>
   </si>
   <si>
+    <t xml:space="preserve">v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FastAPI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">uvicorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29.0 </t>
+  </si>
+  <si>
     <t xml:space="preserve">rule: some may have “default”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fastapi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avicorn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -97,6 +113,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,7 +169,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -173,11 +194,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -304,7 +349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F9"/>
+  <dimension ref="A2:G13"/>
   <sheetFormatPr defaultColWidth="8.48046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.82"/>
@@ -325,6 +370,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
@@ -337,12 +383,18 @@
         <v>4</v>
       </c>
       <c r="F4" s="3"/>
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -355,7 +407,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>22.04</v>
@@ -363,8 +415,8 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="str">
-        <f aca="false">"Dockerfile."&amp;C7&amp;"_"&amp;D7&amp;"_v"&amp;B7</f>
-        <v>Dockerfile.python_3.12-slim_v1</v>
+        <f aca="false">"Dockerfile."&amp;C7&amp;"_"&amp;D7&amp;".v"&amp;B7</f>
+        <v>Dockerfile.python_3.12-slim.v1</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -373,13 +425,16 @@
         <v>4</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="str">
-        <f aca="false">"Dockerfile."&amp;C8&amp;"_"&amp;D8&amp;"_v"&amp;B8</f>
-        <v>Dockerfile.python_3.12-slim_v2</v>
+        <f aca="false">"Dockerfile."&amp;C8&amp;"_"&amp;D8&amp;".v"&amp;B8</f>
+        <v>Dockerfile.python_3.12-slim.v2</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>2</v>
@@ -388,22 +443,104 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="str">
-        <f aca="false">"Dockerfile."&amp;C9&amp;"_"&amp;D9&amp;"_v"&amp;B9</f>
-        <v>Dockerfile.__v3</v>
+        <f aca="false">"Dockerfile."&amp;C9&amp;"_"&amp;D9&amp;".v"&amp;B9</f>
+        <v>Dockerfile.python_3.12-slim.v3</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="str">
+        <f aca="false">"Dockerfile."&amp;C10&amp;"_"&amp;D10&amp;".v"&amp;B10</f>
+        <v>Dockerfile.python_3.12-slim.v4</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="str">
+        <f aca="false">"Dockerfile."&amp;C11&amp;"_"&amp;D11&amp;".v"&amp;B11</f>
+        <v>Dockerfile.python_3.12-slim.v5</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="str">
+        <f aca="false">"Dockerfile."&amp;C12&amp;"_"&amp;D12&amp;".v"&amp;B12</f>
+        <v>Dockerfile.python_3.12-slim.v6</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="str">
+        <f aca="false">"Dockerfile."&amp;C13&amp;"_"&amp;D13&amp;".v"&amp;B13</f>
+        <v>Dockerfile.python_3.12-slim.v7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="E4:F4"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -421,17 +558,41 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B4:B7"/>
+  <dimension ref="A3:C7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="6" width="11.53"/>
+  </cols>
   <sheetData>
+    <row r="3" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6"/>
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6"/>
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2"/>
+      <c r="B7" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -452,17 +613,17 @@
   <dimension ref="B1:E10"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="11.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="24.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="7.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="7.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="7" width="11.55"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="11.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="24.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="7.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="7.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="12" width="11.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="7" t="s">
-        <v>9</v>
+      <c r="B1" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -491,24 +652,24 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>22.04</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
+      <c r="D9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -516,10 +677,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
